--- a/outputs/comparacion_f1_nsb_nsm_con_diff_tiempo.xlsx
+++ b/outputs/comparacion_f1_nsb_nsm_con_diff_tiempo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>nsb_support_minutos</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>nsm_support_minutos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>diff_support_minutos</t>
         </is>
       </c>
@@ -457,16 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.518</v>
+        <v>0.6045</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5899</v>
+        <v>0.7209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.1165</v>
       </c>
       <c r="E2" t="n">
-        <v>5.47</v>
+        <v>24.66</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.24</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3629</v>
+        <v>0.4294</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1973</v>
+        <v>0.2483</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1656</v>
+        <v>-0.1812</v>
       </c>
       <c r="E3" t="n">
-        <v>-20.09</v>
+        <v>27.57</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-13.78</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4564</v>
+        <v>0.5241</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5511</v>
+        <v>0.6806</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1565</v>
       </c>
       <c r="E4" t="n">
-        <v>1.76</v>
+        <v>53.13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="5">
@@ -514,54 +542,47 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3621</v>
+        <v>0.3556</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4326</v>
+        <v>0.4782</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1225</v>
       </c>
       <c r="E5" t="n">
-        <v>1.38</v>
+        <v>19.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SPEECH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6921</v>
+        <v>0.7329</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8027</v>
+        <v>0.7873</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1106</v>
+        <v>0.0544</v>
       </c>
       <c r="E6" t="n">
-        <v>-60.31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SPEECH</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6165</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6645</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-11.69</v>
+        <v>111.37</v>
+      </c>
+      <c r="F6" t="n">
+        <v>106.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-5.2</v>
       </c>
     </row>
   </sheetData>
